--- a/cargo_insurance.xlsx
+++ b/cargo_insurance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733B3D00-ACF1-4712-A676-DC4F68FEF6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D554E3-5FCF-4C86-A09A-17DCE2ABE8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8FB43AA7-AAE4-4BB0-AE80-382DFD6B6D06}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
   <si>
     <t>company</t>
   </si>
@@ -84,13 +84,210 @@
   </si>
   <si>
     <t>02-037-9888 # 225</t>
+  </si>
+  <si>
+    <t>Dhipaya Insurance</t>
+  </si>
+  <si>
+    <t>คุณพัชรลภัส</t>
+  </si>
+  <si>
+    <t>คุณเสาวลักษณ์</t>
+  </si>
+  <si>
+    <t>Patcharalapats@dhipaya.co.th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-2392213 </t>
+  </si>
+  <si>
+    <t>saovalaks@dhipaya.co.th</t>
+  </si>
+  <si>
+    <t>02-2392203</t>
+  </si>
+  <si>
+    <t>Mitsiam Borker (AXA)</t>
+  </si>
+  <si>
+    <t>MitSiam - K.สุเชาว์</t>
+  </si>
+  <si>
+    <t>Axa K. Chanya</t>
+  </si>
+  <si>
+    <t>n.suchao@mitsui.com</t>
+  </si>
+  <si>
+    <t>088-623-0112</t>
+  </si>
+  <si>
+    <t>chanya.po@axa.co.th</t>
+  </si>
+  <si>
+    <t>081-855-7605</t>
+  </si>
+  <si>
+    <t>สอบถามข้อมูล / ค่าเบี้ย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXA K. ธนียา </t>
+  </si>
+  <si>
+    <t>Taneeya.li@axa.co.th</t>
+  </si>
+  <si>
+    <t>02-118-8452</t>
+  </si>
+  <si>
+    <t>แจ้งออกกรมธรรม์</t>
+  </si>
+  <si>
+    <t>AXA K. Sirichan</t>
+  </si>
+  <si>
+    <t>Khun La-ied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thai Star Borker ( Chubb ) </t>
+  </si>
+  <si>
+    <t>ใช้ได้เฉพาะทางแอร์เท่านั้น</t>
+  </si>
+  <si>
+    <t>Sirichan.so@axa.co.th</t>
+  </si>
+  <si>
+    <t>thaistar@tssc.co.th</t>
+  </si>
+  <si>
+    <t>02-679-7600 Ext.2503</t>
+  </si>
+  <si>
+    <t>02-245-4082-3</t>
+  </si>
+  <si>
+    <t>NICE INSURE BROKER (MSIG)</t>
+  </si>
+  <si>
+    <t>PK Inter Consultants (South East)</t>
+  </si>
+  <si>
+    <t>Euro-Thai Broker (Viriyah)</t>
+  </si>
+  <si>
+    <t>Euro-thai K.ฝ้าย</t>
+  </si>
+  <si>
+    <t>Euro-thai K.Patarapong</t>
+  </si>
+  <si>
+    <t>K. มนัสวี</t>
+  </si>
+  <si>
+    <t>tuk_khongphan@hotmail.com</t>
+  </si>
+  <si>
+    <t>087-504-1515</t>
+  </si>
+  <si>
+    <t>K. ขวัญวนา</t>
+  </si>
+  <si>
+    <t>Khwanwana_B@th.msig-asia.com</t>
+  </si>
+  <si>
+    <t>089-457-0036</t>
+  </si>
+  <si>
+    <t>K. Jeeraporn</t>
+  </si>
+  <si>
+    <t>Jeeraporn_M@th.msig-asia.com</t>
+  </si>
+  <si>
+    <t>02-825-8923</t>
+  </si>
+  <si>
+    <t>แจ้งงาน, สอบถามข้อมูล/ค่าเบี้</t>
+  </si>
+  <si>
+    <t>K. Krittaporn</t>
+  </si>
+  <si>
+    <t>krittaporn.k@segroup.co.th</t>
+  </si>
+  <si>
+    <t>02-631-1311 Ext. 5132</t>
+  </si>
+  <si>
+    <t>K. Hhemwarin</t>
+  </si>
+  <si>
+    <t>mk_marine@pkintercon.com</t>
+  </si>
+  <si>
+    <t>02-681-2929</t>
+  </si>
+  <si>
+    <t>(แจ้งงาน/สอบถาม CC. เมล์ด้วยทุกครั้ง)
+mk_marine@pkintercon.com,
+Thanida.s@segroup.co.th,</t>
+  </si>
+  <si>
+    <t>Viriyah K.แคท</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> แจ้งออกกรมธรรม์</t>
+  </si>
+  <si>
+    <t>marine_und@viriyah.co.th</t>
+  </si>
+  <si>
+    <t>support@eurothaibroker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> แจ้งงาน CC. เมล์นี้ด้วยทุกครั้ง</t>
+  </si>
+  <si>
+    <t>patarapong@eurothaibroker.com</t>
+  </si>
+  <si>
+    <t>086-374-6595, 02-514-3214-6</t>
+  </si>
+  <si>
+    <t>Muang Thai Insurance</t>
+  </si>
+  <si>
+    <t>แจ้งออกกรมธรรม์ CC ทุกครั้ง MiscellaneousUnderwriting-MarineInsurance@muangthaiinsurance.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">คุณ ณัฏฐณิชา </t>
+  </si>
+  <si>
+    <t>แจ้งออกกรมธรรม์ / สอบถามข้อมูล / ค่าเบี้ย</t>
+  </si>
+  <si>
+    <t>nattanicha.tr@muangthaiinsurance.com</t>
+  </si>
+  <si>
+    <t>02-290-3333 Ex. 3558</t>
+  </si>
+  <si>
+    <t>คุณ จีรภา</t>
+  </si>
+  <si>
+    <t>jeerapa.w@muangthaiinsurance.com</t>
+  </si>
+  <si>
+    <t>081-298-2426</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +298,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,10 +328,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -140,8 +346,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -474,14 +697,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E741C3F-2DFD-4F6F-AA50-8B601100C0CB}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -505,7 +730,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -514,7 +739,7 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
@@ -522,23 +747,305 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="7"/>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="7"/>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="7"/>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="7"/>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="7"/>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="7"/>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="7"/>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="7"/>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="7"/>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A15"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{466B4215-126D-4DDE-8FCF-B99BCB139AA4}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{DBB5ED0D-9BE8-495B-9E7D-D0C76B5F9474}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{A8D363C8-DACE-4684-A9D5-9BA7AC3A509A}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{F938C370-2F3E-4C64-9739-20A9FAF988E0}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{DDBE33A4-2DD2-4852-839B-0B06DDAAEF16}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{FF8B1DC0-B19D-45EB-B5C1-C471A58613C3}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{064A0233-22B0-4D8A-B044-A6BC38BE8CAB}"/>
+    <hyperlink ref="D11" r:id="rId8" xr:uid="{CB84CAFE-EB4C-4BAF-80B7-F50978F0F7E2}"/>
+    <hyperlink ref="D12" r:id="rId9" xr:uid="{DB7E34FE-4828-4797-8D09-1D143B509EF0}"/>
+    <hyperlink ref="D2" r:id="rId10" xr:uid="{F81A75FF-02C9-446A-AEEC-E21C915D3CEF}"/>
+    <hyperlink ref="D3" r:id="rId11" xr:uid="{123C6B41-173C-4D27-BD6A-E6186F30D314}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{22ED7CF5-64D8-4CA7-8360-CA32477247AC}"/>
+    <hyperlink ref="D14" r:id="rId13" xr:uid="{E5B6B090-0644-432A-9ACB-B9D090A5AD08}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{5FB35608-DAE7-4BC3-995D-49F54B59CEE5}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{C803B231-F8A3-45EF-AB04-AD50CB88D0A5}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{7E499154-732D-478F-BDA3-40DCA4B7869D}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{20AD176B-CD45-4E93-9B32-48305C99AC32}"/>
+    <hyperlink ref="D19" r:id="rId18" xr:uid="{79316197-9234-46FA-ABD0-DB5441E4C375}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{03DBA5B9-2877-47BD-B702-4707D45B6F90}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cargo_insurance.xlsx
+++ b/cargo_insurance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D554E3-5FCF-4C86-A09A-17DCE2ABE8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B25E029-5E42-4344-A2AD-BF61354C4244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8FB43AA7-AAE4-4BB0-AE80-382DFD6B6D06}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
   <si>
     <t>company</t>
   </si>
@@ -332,7 +332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -348,19 +348,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -730,7 +721,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -747,7 +738,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
@@ -762,7 +755,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
@@ -776,7 +769,9 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
@@ -788,7 +783,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
@@ -802,7 +797,9 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
@@ -814,7 +811,9 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -829,7 +828,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
@@ -861,10 +862,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="6"/>
       <c r="C11" t="s">
         <v>47</v>
       </c>
@@ -876,7 +877,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
+      <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
@@ -891,7 +894,9 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
+      <c r="A13" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
@@ -905,8 +910,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B14" t="s">
@@ -921,12 +926,14 @@
       <c r="E14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
+    <row r="15" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="C15" t="s">
         <v>60</v>
       </c>
@@ -936,10 +943,12 @@
       <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B16" t="s">
@@ -951,35 +960,39 @@
       <c r="D16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>70</v>
-      </c>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
+      <c r="A17" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="C17" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="10"/>
+      <c r="E17" s="3"/>
       <c r="F17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
+      <c r="A18" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="C18" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B19" t="s">
@@ -999,7 +1012,9 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
+      <c r="A20" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="B20" t="s">
         <v>29</v>
       </c>
@@ -1014,17 +1029,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A15"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{466B4215-126D-4DDE-8FCF-B99BCB139AA4}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{DBB5ED0D-9BE8-495B-9E7D-D0C76B5F9474}"/>

--- a/cargo_insurance.xlsx
+++ b/cargo_insurance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B25E029-5E42-4344-A2AD-BF61354C4244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7172B91A-15DE-4C91-BD22-374D90865707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8FB43AA7-AAE4-4BB0-AE80-382DFD6B6D06}"/>
   </bookViews>
